--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -5089,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117592259</v>
+        <v>117592087</v>
       </c>
       <c r="B44" t="n">
-        <v>97836</v>
+        <v>90941</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5105,50 +5105,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572791</v>
+        <v>572758</v>
       </c>
       <c r="R44" t="n">
-        <v>6701836</v>
+        <v>6701840</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5189,7 +5173,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5208,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117592087</v>
+        <v>117592259</v>
       </c>
       <c r="B45" t="n">
-        <v>90941</v>
+        <v>97836</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5224,34 +5207,50 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572758</v>
+        <v>572791</v>
       </c>
       <c r="R45" t="n">
-        <v>6701840</v>
+        <v>6701836</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5292,6 +5291,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117592095</v>
+        <v>117592088</v>
       </c>
       <c r="B46" t="n">
-        <v>97836</v>
+        <v>90782</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5322,25 +5322,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572776</v>
+        <v>572749</v>
       </c>
       <c r="R46" t="n">
-        <v>6701792</v>
+        <v>6701721</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5412,7 +5412,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117592261</v>
+        <v>117592095</v>
       </c>
       <c r="B47" t="n">
         <v>97836</v>
@@ -5445,29 +5445,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572837</v>
+        <v>572776</v>
       </c>
       <c r="R47" t="n">
-        <v>6701775</v>
+        <v>6701792</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5508,7 +5496,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5527,10 +5514,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117592088</v>
+        <v>117592261</v>
       </c>
       <c r="B48" t="n">
-        <v>90782</v>
+        <v>97836</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5539,38 +5526,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572749</v>
+        <v>572837</v>
       </c>
       <c r="R48" t="n">
-        <v>6701721</v>
+        <v>6701775</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5611,6 +5610,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5833,10 +5833,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117592075</v>
+        <v>117592254</v>
       </c>
       <c r="B51" t="n">
-        <v>90499</v>
+        <v>97836</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5845,38 +5845,54 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572748</v>
+        <v>572828</v>
       </c>
       <c r="R51" t="n">
-        <v>6701722</v>
+        <v>6701791</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5917,6 +5933,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6037,10 +6054,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117592254</v>
+        <v>117592075</v>
       </c>
       <c r="B53" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6049,54 +6066,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572828</v>
+        <v>572748</v>
       </c>
       <c r="R53" t="n">
-        <v>6701791</v>
+        <v>6701722</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6137,7 +6138,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6875,10 +6875,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117592074</v>
+        <v>117592070</v>
       </c>
       <c r="B61" t="n">
-        <v>90499</v>
+        <v>90464</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6887,25 +6887,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572715</v>
+        <v>572871</v>
       </c>
       <c r="R61" t="n">
-        <v>6701718</v>
+        <v>6701800</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6977,10 +6977,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117592070</v>
+        <v>117592074</v>
       </c>
       <c r="B62" t="n">
-        <v>90464</v>
+        <v>90499</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6989,25 +6989,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572871</v>
+        <v>572715</v>
       </c>
       <c r="R62" t="n">
-        <v>6701800</v>
+        <v>6701718</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -4885,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117592068</v>
+        <v>117592089</v>
       </c>
       <c r="B42" t="n">
-        <v>90464</v>
+        <v>90782</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4897,25 +4897,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572776</v>
+        <v>572636</v>
       </c>
       <c r="R42" t="n">
-        <v>6701638</v>
+        <v>6701807</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117592071</v>
+        <v>117592085</v>
       </c>
       <c r="B43" t="n">
-        <v>90464</v>
+        <v>57303</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4999,25 +4999,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572850</v>
+        <v>572718</v>
       </c>
       <c r="R43" t="n">
-        <v>6701817</v>
+        <v>6701702</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117592087</v>
+        <v>117592096</v>
       </c>
       <c r="B44" t="n">
-        <v>90941</v>
+        <v>97836</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5105,21 +5105,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572758</v>
+        <v>572757</v>
       </c>
       <c r="R44" t="n">
-        <v>6701840</v>
+        <v>6701796</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117592088</v>
+        <v>117592092</v>
       </c>
       <c r="B46" t="n">
-        <v>90782</v>
+        <v>90890</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5326,21 +5326,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5350,10 +5345,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572749</v>
+        <v>572758</v>
       </c>
       <c r="R46" t="n">
-        <v>6701721</v>
+        <v>6701797</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5412,10 +5407,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117592095</v>
+        <v>117592073</v>
       </c>
       <c r="B47" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5424,25 +5419,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5452,10 +5447,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572776</v>
+        <v>572719</v>
       </c>
       <c r="R47" t="n">
-        <v>6701792</v>
+        <v>6701704</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5514,7 +5509,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117592261</v>
+        <v>117592260</v>
       </c>
       <c r="B48" t="n">
         <v>97836</v>
@@ -5549,7 +5544,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5566,10 +5561,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572837</v>
+        <v>572844</v>
       </c>
       <c r="R48" t="n">
-        <v>6701775</v>
+        <v>6701792</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5629,10 +5624,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117592073</v>
+        <v>117592069</v>
       </c>
       <c r="B49" t="n">
-        <v>90499</v>
+        <v>90464</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5641,25 +5636,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572719</v>
+        <v>572651</v>
       </c>
       <c r="R49" t="n">
-        <v>6701704</v>
+        <v>6701792</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5833,10 +5828,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117592254</v>
+        <v>117592075</v>
       </c>
       <c r="B51" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5845,54 +5840,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572828</v>
+        <v>572748</v>
       </c>
       <c r="R51" t="n">
-        <v>6701791</v>
+        <v>6701722</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5933,7 +5912,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5952,10 +5930,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117592086</v>
+        <v>117592254</v>
       </c>
       <c r="B52" t="n">
-        <v>90941</v>
+        <v>97836</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5968,34 +5946,50 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572849</v>
+        <v>572828</v>
       </c>
       <c r="R52" t="n">
-        <v>6701826</v>
+        <v>6701791</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6036,6 +6030,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6054,10 +6049,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117592075</v>
+        <v>117592095</v>
       </c>
       <c r="B53" t="n">
-        <v>90499</v>
+        <v>97836</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6066,25 +6061,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6094,10 +6089,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572748</v>
+        <v>572776</v>
       </c>
       <c r="R53" t="n">
-        <v>6701722</v>
+        <v>6701792</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6156,7 +6151,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117592078</v>
+        <v>117592074</v>
       </c>
       <c r="B54" t="n">
         <v>90499</v>
@@ -6196,10 +6191,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572750</v>
+        <v>572715</v>
       </c>
       <c r="R54" t="n">
-        <v>6701813</v>
+        <v>6701718</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6258,10 +6253,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117592094</v>
+        <v>117592099</v>
       </c>
       <c r="B55" t="n">
-        <v>97836</v>
+        <v>104929</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6270,25 +6265,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6298,10 +6293,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572966</v>
+        <v>572850</v>
       </c>
       <c r="R55" t="n">
-        <v>6701719</v>
+        <v>6701825</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6360,10 +6355,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117592089</v>
+        <v>117592094</v>
       </c>
       <c r="B56" t="n">
-        <v>90782</v>
+        <v>97836</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6372,25 +6367,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6400,10 +6395,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572636</v>
+        <v>572966</v>
       </c>
       <c r="R56" t="n">
-        <v>6701807</v>
+        <v>6701719</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6462,7 +6457,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117592092</v>
+        <v>117592093</v>
       </c>
       <c r="B57" t="n">
         <v>90890</v>
@@ -6497,10 +6492,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572758</v>
+        <v>572889</v>
       </c>
       <c r="R57" t="n">
-        <v>6701797</v>
+        <v>6701656</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6661,10 +6656,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117592083</v>
+        <v>117592258</v>
       </c>
       <c r="B59" t="n">
-        <v>4763</v>
+        <v>97836</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6673,36 +6668,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6710,10 +6708,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572772</v>
+        <v>572820</v>
       </c>
       <c r="R59" t="n">
-        <v>6701818</v>
+        <v>6701792</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6773,10 +6771,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117592079</v>
+        <v>117592255</v>
       </c>
       <c r="B60" t="n">
-        <v>90499</v>
+        <v>97836</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6785,38 +6783,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572839</v>
+        <v>572888</v>
       </c>
       <c r="R60" t="n">
-        <v>6701831</v>
+        <v>6701664</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6857,6 +6867,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6875,10 +6886,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117592070</v>
+        <v>117592072</v>
       </c>
       <c r="B61" t="n">
-        <v>90464</v>
+        <v>90499</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6887,25 +6898,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6915,10 +6926,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572871</v>
+        <v>572712</v>
       </c>
       <c r="R61" t="n">
-        <v>6701800</v>
+        <v>6701702</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6977,7 +6988,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117592074</v>
+        <v>117592076</v>
       </c>
       <c r="B62" t="n">
         <v>90499</v>
@@ -7017,10 +7028,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572715</v>
+        <v>572656</v>
       </c>
       <c r="R62" t="n">
-        <v>6701718</v>
+        <v>6701796</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7079,10 +7090,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117592069</v>
+        <v>117592261</v>
       </c>
       <c r="B63" t="n">
-        <v>90464</v>
+        <v>97836</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7091,38 +7102,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572651</v>
+        <v>572837</v>
       </c>
       <c r="R63" t="n">
-        <v>6701792</v>
+        <v>6701775</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7163,6 +7186,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7181,10 +7205,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117592076</v>
+        <v>117592083</v>
       </c>
       <c r="B64" t="n">
-        <v>90499</v>
+        <v>4763</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7193,38 +7217,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572656</v>
+        <v>572772</v>
       </c>
       <c r="R64" t="n">
-        <v>6701796</v>
+        <v>6701818</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7265,6 +7298,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7283,10 +7317,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117592085</v>
+        <v>117592071</v>
       </c>
       <c r="B65" t="n">
-        <v>57303</v>
+        <v>90464</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7295,25 +7329,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7323,10 +7357,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572718</v>
+        <v>572850</v>
       </c>
       <c r="R65" t="n">
-        <v>6701702</v>
+        <v>6701817</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7385,10 +7419,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117592260</v>
+        <v>117592070</v>
       </c>
       <c r="B66" t="n">
-        <v>97836</v>
+        <v>90464</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7397,50 +7431,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572844</v>
+        <v>572871</v>
       </c>
       <c r="R66" t="n">
-        <v>6701792</v>
+        <v>6701800</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7481,7 +7503,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7500,7 +7521,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117592072</v>
+        <v>117592078</v>
       </c>
       <c r="B67" t="n">
         <v>90499</v>
@@ -7540,10 +7561,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572712</v>
+        <v>572750</v>
       </c>
       <c r="R67" t="n">
-        <v>6701702</v>
+        <v>6701813</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7602,10 +7623,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117592255</v>
+        <v>117592068</v>
       </c>
       <c r="B68" t="n">
-        <v>97836</v>
+        <v>90464</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7614,50 +7635,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572888</v>
+        <v>572776</v>
       </c>
       <c r="R68" t="n">
-        <v>6701664</v>
+        <v>6701638</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7698,7 +7707,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7717,10 +7725,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117592258</v>
+        <v>117592088</v>
       </c>
       <c r="B69" t="n">
-        <v>97836</v>
+        <v>90782</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7729,50 +7737,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>572820</v>
+        <v>572749</v>
       </c>
       <c r="R69" t="n">
-        <v>6701792</v>
+        <v>6701721</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7813,7 +7809,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7832,10 +7827,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117592096</v>
+        <v>117592087</v>
       </c>
       <c r="B70" t="n">
-        <v>97836</v>
+        <v>90941</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7848,21 +7843,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7872,10 +7867,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>572757</v>
+        <v>572758</v>
       </c>
       <c r="R70" t="n">
-        <v>6701796</v>
+        <v>6701840</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7934,10 +7929,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117592093</v>
+        <v>117592079</v>
       </c>
       <c r="B71" t="n">
-        <v>90890</v>
+        <v>90499</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7950,16 +7945,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>572889</v>
+        <v>572839</v>
       </c>
       <c r="R71" t="n">
-        <v>6701656</v>
+        <v>6701831</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8031,10 +8031,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117592099</v>
+        <v>117592086</v>
       </c>
       <c r="B72" t="n">
-        <v>104929</v>
+        <v>90941</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8043,25 +8043,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>572850</v>
+        <v>572849</v>
       </c>
       <c r="R72" t="n">
-        <v>6701825</v>
+        <v>6701826</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -4885,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117592089</v>
+        <v>117592100</v>
       </c>
       <c r="B42" t="n">
-        <v>90782</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4901,21 +4901,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572636</v>
+        <v>572898</v>
       </c>
       <c r="R42" t="n">
-        <v>6701807</v>
+        <v>6701764</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117592085</v>
+        <v>117592255</v>
       </c>
       <c r="B43" t="n">
-        <v>57303</v>
+        <v>97838</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4999,38 +4999,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572718</v>
+        <v>572888</v>
       </c>
       <c r="R43" t="n">
-        <v>6701702</v>
+        <v>6701664</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5071,6 +5083,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5089,10 +5102,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117592096</v>
+        <v>117592086</v>
       </c>
       <c r="B44" t="n">
-        <v>97836</v>
+        <v>90943</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5105,21 +5118,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5142,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572757</v>
+        <v>572849</v>
       </c>
       <c r="R44" t="n">
-        <v>6701796</v>
+        <v>6701826</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5191,10 +5204,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117592259</v>
+        <v>117592068</v>
       </c>
       <c r="B45" t="n">
-        <v>97836</v>
+        <v>90466</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5203,54 +5216,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572791</v>
+        <v>572776</v>
       </c>
       <c r="R45" t="n">
-        <v>6701836</v>
+        <v>6701638</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5291,7 +5288,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5310,10 +5306,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117592092</v>
+        <v>117592093</v>
       </c>
       <c r="B46" t="n">
-        <v>90890</v>
+        <v>90892</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5345,10 +5341,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572758</v>
+        <v>572889</v>
       </c>
       <c r="R46" t="n">
-        <v>6701797</v>
+        <v>6701656</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5407,10 +5403,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117592073</v>
+        <v>117592260</v>
       </c>
       <c r="B47" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5419,38 +5415,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572719</v>
+        <v>572844</v>
       </c>
       <c r="R47" t="n">
-        <v>6701704</v>
+        <v>6701792</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5491,6 +5499,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5509,10 +5518,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117592260</v>
+        <v>117592077</v>
       </c>
       <c r="B48" t="n">
-        <v>97836</v>
+        <v>90501</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5521,50 +5530,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572844</v>
+        <v>572850</v>
       </c>
       <c r="R48" t="n">
-        <v>6701792</v>
+        <v>6701811</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5605,7 +5602,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5624,10 +5620,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117592069</v>
+        <v>117592261</v>
       </c>
       <c r="B49" t="n">
-        <v>90464</v>
+        <v>97838</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5636,38 +5632,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572651</v>
+        <v>572837</v>
       </c>
       <c r="R49" t="n">
-        <v>6701792</v>
+        <v>6701775</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5708,6 +5716,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5726,10 +5735,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117592077</v>
+        <v>117592083</v>
       </c>
       <c r="B50" t="n">
-        <v>90499</v>
+        <v>4763</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5738,38 +5747,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572850</v>
+        <v>572772</v>
       </c>
       <c r="R50" t="n">
-        <v>6701811</v>
+        <v>6701818</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5810,6 +5828,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5828,10 +5847,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117592075</v>
+        <v>117592085</v>
       </c>
       <c r="B51" t="n">
-        <v>90499</v>
+        <v>57304</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5844,21 +5863,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5868,10 +5887,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572748</v>
+        <v>572718</v>
       </c>
       <c r="R51" t="n">
-        <v>6701722</v>
+        <v>6701702</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5930,10 +5949,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117592254</v>
+        <v>117592092</v>
       </c>
       <c r="B52" t="n">
-        <v>97836</v>
+        <v>90892</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5942,54 +5961,33 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572828</v>
+        <v>572758</v>
       </c>
       <c r="R52" t="n">
-        <v>6701791</v>
+        <v>6701797</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6030,7 +6028,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6049,10 +6046,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117592095</v>
+        <v>117592099</v>
       </c>
       <c r="B53" t="n">
-        <v>97836</v>
+        <v>104931</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6061,25 +6058,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6089,10 +6086,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572776</v>
+        <v>572850</v>
       </c>
       <c r="R53" t="n">
-        <v>6701792</v>
+        <v>6701825</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6154,7 +6151,7 @@
         <v>117592074</v>
       </c>
       <c r="B54" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6253,10 +6250,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117592099</v>
+        <v>117592076</v>
       </c>
       <c r="B55" t="n">
-        <v>104929</v>
+        <v>90501</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6265,25 +6262,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6293,10 +6290,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572850</v>
+        <v>572656</v>
       </c>
       <c r="R55" t="n">
-        <v>6701825</v>
+        <v>6701796</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6355,10 +6352,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117592094</v>
+        <v>117592078</v>
       </c>
       <c r="B56" t="n">
-        <v>97836</v>
+        <v>90501</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6367,25 +6364,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6395,10 +6392,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>572966</v>
+        <v>572750</v>
       </c>
       <c r="R56" t="n">
-        <v>6701719</v>
+        <v>6701813</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6457,10 +6454,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117592093</v>
+        <v>117592079</v>
       </c>
       <c r="B57" t="n">
-        <v>90890</v>
+        <v>90501</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6473,16 +6470,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6492,10 +6494,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572889</v>
+        <v>572839</v>
       </c>
       <c r="R57" t="n">
-        <v>6701656</v>
+        <v>6701831</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6554,10 +6556,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117592100</v>
+        <v>117592073</v>
       </c>
       <c r="B58" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6570,21 +6572,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6594,10 +6596,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572898</v>
+        <v>572719</v>
       </c>
       <c r="R58" t="n">
-        <v>6701764</v>
+        <v>6701704</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6656,10 +6658,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117592258</v>
+        <v>117592070</v>
       </c>
       <c r="B59" t="n">
-        <v>97836</v>
+        <v>90466</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6668,50 +6670,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>572820</v>
+        <v>572871</v>
       </c>
       <c r="R59" t="n">
-        <v>6701792</v>
+        <v>6701800</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6752,7 +6742,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6771,10 +6760,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117592255</v>
+        <v>117592096</v>
       </c>
       <c r="B60" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6804,29 +6793,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572888</v>
+        <v>572757</v>
       </c>
       <c r="R60" t="n">
-        <v>6701664</v>
+        <v>6701796</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6867,7 +6844,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6886,10 +6862,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117592072</v>
+        <v>117592094</v>
       </c>
       <c r="B61" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6898,25 +6874,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6926,10 +6902,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572712</v>
+        <v>572966</v>
       </c>
       <c r="R61" t="n">
-        <v>6701702</v>
+        <v>6701719</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6988,10 +6964,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117592076</v>
+        <v>117592087</v>
       </c>
       <c r="B62" t="n">
-        <v>90499</v>
+        <v>90943</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7000,25 +6976,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7028,10 +7004,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>572656</v>
+        <v>572758</v>
       </c>
       <c r="R62" t="n">
-        <v>6701796</v>
+        <v>6701840</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7090,10 +7066,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117592261</v>
+        <v>117592254</v>
       </c>
       <c r="B63" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7125,7 +7101,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7133,7 +7109,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -7142,10 +7122,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>572837</v>
+        <v>572828</v>
       </c>
       <c r="R63" t="n">
-        <v>6701775</v>
+        <v>6701791</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7205,10 +7185,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117592083</v>
+        <v>117592075</v>
       </c>
       <c r="B64" t="n">
-        <v>4763</v>
+        <v>90501</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7217,47 +7197,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>572772</v>
+        <v>572748</v>
       </c>
       <c r="R64" t="n">
-        <v>6701818</v>
+        <v>6701722</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7298,7 +7269,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7317,10 +7287,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117592071</v>
+        <v>117592069</v>
       </c>
       <c r="B65" t="n">
-        <v>90464</v>
+        <v>90466</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7357,10 +7327,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>572850</v>
+        <v>572651</v>
       </c>
       <c r="R65" t="n">
-        <v>6701817</v>
+        <v>6701792</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7419,10 +7389,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117592070</v>
+        <v>117592259</v>
       </c>
       <c r="B66" t="n">
-        <v>90464</v>
+        <v>97838</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7431,38 +7401,54 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572871</v>
+        <v>572791</v>
       </c>
       <c r="R66" t="n">
-        <v>6701800</v>
+        <v>6701836</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7503,6 +7489,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7521,10 +7508,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117592078</v>
+        <v>117592088</v>
       </c>
       <c r="B67" t="n">
-        <v>90499</v>
+        <v>90784</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7537,21 +7524,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7561,10 +7548,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572750</v>
+        <v>572749</v>
       </c>
       <c r="R67" t="n">
-        <v>6701813</v>
+        <v>6701721</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7623,10 +7610,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117592068</v>
+        <v>117592258</v>
       </c>
       <c r="B68" t="n">
-        <v>90464</v>
+        <v>97838</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7635,38 +7622,50 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572776</v>
+        <v>572820</v>
       </c>
       <c r="R68" t="n">
-        <v>6701638</v>
+        <v>6701792</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7707,6 +7706,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7725,10 +7725,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117592088</v>
+        <v>117592071</v>
       </c>
       <c r="B69" t="n">
-        <v>90782</v>
+        <v>90466</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7737,25 +7737,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7765,10 +7765,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>572749</v>
+        <v>572850</v>
       </c>
       <c r="R69" t="n">
-        <v>6701721</v>
+        <v>6701817</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7827,10 +7827,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117592087</v>
+        <v>117592072</v>
       </c>
       <c r="B70" t="n">
-        <v>90941</v>
+        <v>90501</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7839,25 +7839,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>572758</v>
+        <v>572712</v>
       </c>
       <c r="R70" t="n">
-        <v>6701840</v>
+        <v>6701702</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7929,10 +7929,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117592079</v>
+        <v>117592095</v>
       </c>
       <c r="B71" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7941,25 +7941,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>572839</v>
+        <v>572776</v>
       </c>
       <c r="R71" t="n">
-        <v>6701831</v>
+        <v>6701792</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8031,10 +8031,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117592086</v>
+        <v>117592089</v>
       </c>
       <c r="B72" t="n">
-        <v>90941</v>
+        <v>90784</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8043,25 +8043,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>572849</v>
+        <v>572636</v>
       </c>
       <c r="R72" t="n">
-        <v>6701826</v>
+        <v>6701807</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -5847,10 +5847,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117592085</v>
+        <v>117592092</v>
       </c>
       <c r="B51" t="n">
-        <v>57304</v>
+        <v>90892</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5863,21 +5863,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5887,10 +5882,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572718</v>
+        <v>572758</v>
       </c>
       <c r="R51" t="n">
-        <v>6701702</v>
+        <v>6701797</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5949,10 +5944,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117592092</v>
+        <v>117592085</v>
       </c>
       <c r="B52" t="n">
-        <v>90892</v>
+        <v>57304</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5965,16 +5960,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572758</v>
+        <v>572718</v>
       </c>
       <c r="R52" t="n">
-        <v>6701797</v>
+        <v>6701702</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6454,10 +6454,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117592079</v>
+        <v>117592096</v>
       </c>
       <c r="B57" t="n">
-        <v>90501</v>
+        <v>97838</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6466,25 +6466,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6494,10 +6494,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>572839</v>
+        <v>572757</v>
       </c>
       <c r="R57" t="n">
-        <v>6701831</v>
+        <v>6701796</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117592073</v>
+        <v>117592094</v>
       </c>
       <c r="B58" t="n">
-        <v>90501</v>
+        <v>97838</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6568,25 +6568,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>572719</v>
+        <v>572966</v>
       </c>
       <c r="R58" t="n">
-        <v>6701704</v>
+        <v>6701719</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6760,10 +6760,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117592096</v>
+        <v>117592079</v>
       </c>
       <c r="B60" t="n">
-        <v>97838</v>
+        <v>90501</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6772,25 +6772,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>572757</v>
+        <v>572839</v>
       </c>
       <c r="R60" t="n">
-        <v>6701796</v>
+        <v>6701831</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6862,10 +6862,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117592094</v>
+        <v>117592073</v>
       </c>
       <c r="B61" t="n">
-        <v>97838</v>
+        <v>90501</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6874,25 +6874,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6902,10 +6902,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>572966</v>
+        <v>572719</v>
       </c>
       <c r="R61" t="n">
-        <v>6701719</v>
+        <v>6701704</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7389,10 +7389,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117592259</v>
+        <v>117592088</v>
       </c>
       <c r="B66" t="n">
-        <v>97838</v>
+        <v>90784</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7401,54 +7401,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>572791</v>
+        <v>572749</v>
       </c>
       <c r="R66" t="n">
-        <v>6701836</v>
+        <v>6701721</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7489,7 +7473,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7508,10 +7491,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117592088</v>
+        <v>117592259</v>
       </c>
       <c r="B67" t="n">
-        <v>90784</v>
+        <v>97838</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7520,38 +7503,54 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>572749</v>
+        <v>572791</v>
       </c>
       <c r="R67" t="n">
-        <v>6701721</v>
+        <v>6701836</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7592,6 +7591,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7610,10 +7610,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117592258</v>
+        <v>117592071</v>
       </c>
       <c r="B68" t="n">
-        <v>97838</v>
+        <v>90466</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7622,50 +7622,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>572820</v>
+        <v>572850</v>
       </c>
       <c r="R68" t="n">
-        <v>6701792</v>
+        <v>6701817</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7706,7 +7694,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7725,10 +7712,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117592071</v>
+        <v>117592072</v>
       </c>
       <c r="B69" t="n">
-        <v>90466</v>
+        <v>90501</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7737,25 +7724,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7765,10 +7752,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>572850</v>
+        <v>572712</v>
       </c>
       <c r="R69" t="n">
-        <v>6701817</v>
+        <v>6701702</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7827,10 +7814,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117592072</v>
+        <v>117592258</v>
       </c>
       <c r="B70" t="n">
-        <v>90501</v>
+        <v>97838</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7839,38 +7826,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Skurtjärn, Gstr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>572712</v>
+        <v>572820</v>
       </c>
       <c r="R70" t="n">
-        <v>6701702</v>
+        <v>6701792</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7911,6 +7910,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -8133,10 +8133,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119725119</v>
+        <v>119724708</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8176,21 +8176,16 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skurtjärnen, Skurtjärnen, Gstr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>572850</v>
+        <v>572871</v>
       </c>
       <c r="R73" t="n">
-        <v>6701802</v>
+        <v>6701638</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8222,7 +8217,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8232,7 +8227,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8259,10 +8254,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119724708</v>
+        <v>119725119</v>
       </c>
       <c r="B74" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8302,16 +8297,21 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skurtjärnen, Skurtjärnen, Gstr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>572871</v>
+        <v>572850</v>
       </c>
       <c r="R74" t="n">
-        <v>6701638</v>
+        <v>6701802</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -3300,11 +3300,11 @@
         <v>116167227</v>
       </c>
       <c r="B27" t="n">
-        <v>57265</v>
+        <v>57369</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -3300,7 +3300,7 @@
         <v>116167227</v>
       </c>
       <c r="B27" t="n">
-        <v>57369</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -3300,7 +3300,7 @@
         <v>116167227</v>
       </c>
       <c r="B27" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -3315,11 +3315,6 @@
       <c r="E27" t="n">
         <v>100109</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>

--- a/artfynd/A 60420-2023 artfynd.xlsx
+++ b/artfynd/A 60420-2023 artfynd.xlsx
@@ -3300,7 +3300,7 @@
         <v>116167227</v>
       </c>
       <c r="B27" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3314,6 +3314,11 @@
       </c>
       <c r="E27" t="n">
         <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
